--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-J48-ProfessionNonPS-CISIS.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-J48-ProfessionNonPS-CISIS.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240426120000</t>
+    <t>20241120120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -53,7 +53,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>retired</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-26T12:00:00+01:00</t>
+    <t>2024-11-20T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-J48-ProfessionNonPS-CISIS.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-J48-ProfessionNonPS-CISIS.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20241120120000</t>
+    <t>20240426120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -53,7 +53,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>retired</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-20T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-J48-ProfessionNonPS-CISIS.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-J48-ProfessionNonPS-CISIS.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20240426120000</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Name</t>
@@ -53,7 +53,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>retired</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-26T12:00:00+01:00</t>
+    <t>2024-11-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
